--- a/data/employees/EMP054/AST-EMP054-06.xlsx
+++ b/data/employees/EMP054/AST-EMP054-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Morgan Smith (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Specialist | Location: Fremont | Date: 2025-03-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP054</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp054 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>87</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP054</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp054 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>85</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP054</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp054 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP054</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp054 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>83</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>98</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>85</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>96</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>62</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>71</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>87</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>91</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>76</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>92</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>73</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp054 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>86</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP054</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP054 contributes to ast emp054 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>